--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,11 +87,10 @@
     <t>Generisk profil för medicinsk historik inom mödravård mappat från RIVTA-tjänstekontraktet
 GetMaternityMedicalHistory (clinicalprocess:healthcond:actoutcome v2.0).
 Täcker NPÖ 2.0 och 1177 Journal 2.0.
-OBS: TKBn har tre separata sektioner (registrationRecord, pregnancyCheckupRecord,
-postDeliveryRecord) med egna sektionsspecifika fält. En Observation skapas per sektion
-med Observation.code som diskriminator (se MAT-001 i mapping-issues). Fältnamnen
-i ^short nedan refererar till sektionsspecifika element – implementatören väljer rätt
-sektionselement baserat på Observation.code.</t>
+TKB:n har tre avsnitt (registrationRecord, pregnancyCheckupRecord, postDeliveryRecord).
+Profilen används både för den grupperande Observationen per avsnitt (code = avsnittskod,
+code.text = documentTitle, hasMember = fälten) och för medlems-Observationerna, en per
+fält (MAT-001).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -810,7 +809,7 @@
 </t>
   </si>
   <si>
-    <t>Sektionskod – diskriminator för vilken av de tre sektionerna som Observation representerar</t>
+    <t>Grupperande: avsnittskod med code.text = documentTitle (MAT-003). Medlem: fältets kod</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -1022,7 +1021,7 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>Sektionsspecifikt mätvärde (t.ex. pregnancyCheckupRecord.bloodPressure, postDeliveryRecord.birthWeight)</t>
+    <t>Medlem: fältets värde (t.ex. pregnancyCheckupRecord.bloodPressureSystolic). Grupperande: inget värde</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1434,7 +1433,7 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
+    <t>Grupperande: avsnittets medlems-Observationer (MAT-001)</t>
   </si>
   <si>
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
@@ -1471,7 +1470,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>Sektionsspecifika delfält kodas som component (se MAT-001)</t>
+    <t>Medlem för upprepad post (t.ex. previousGravidityAndParity[i]): postens fält</t>
   </si>
   <si>
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
@@ -7699,7 +7698,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>448</v>
       </c>
@@ -7718,7 +7717,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationMaternity.xlsx
+++ b/StructureDefinition-SEEHDSObservationMaternity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1321,6 +1321,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7077,7 +7081,7 @@
         <v>415</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7086,10 +7090,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7100,10 +7104,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7129,10 +7133,10 @@
         <v>412</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7183,7 +7187,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7195,7 +7199,7 @@
         <v>415</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7204,10 +7208,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7218,10 +7222,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7247,16 +7251,16 @@
         <v>241</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7284,10 +7288,10 @@
         <v>173</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7305,7 +7309,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7323,10 +7327,10 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>348</v>
@@ -7340,10 +7344,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7369,16 +7373,16 @@
         <v>241</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7406,10 +7410,10 @@
         <v>159</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7427,7 +7431,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7445,10 +7449,10 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>348</v>
@@ -7462,10 +7466,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7488,17 +7492,17 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7547,7 +7551,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7571,7 +7575,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7582,10 +7586,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7611,10 +7615,10 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7665,7 +7669,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7686,10 +7690,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7700,10 +7704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7726,16 +7730,16 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7785,7 +7789,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7806,10 +7810,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7820,10 +7824,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7846,16 +7850,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7905,7 +7909,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7926,10 +7930,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7940,10 +7944,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7969,16 +7973,16 @@
         <v>396</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8027,7 +8031,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8048,10 +8052,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8062,10 +8066,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8180,10 +8184,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8300,10 +8304,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8422,10 +8426,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8451,13 +8455,13 @@
         <v>241</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>255</v>
@@ -8509,7 +8513,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>93</v>
@@ -8527,7 +8531,7 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>260</v>
@@ -8544,10 +8548,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8573,13 +8577,13 @@
         <v>319</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>321</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>323</v>
@@ -8631,7 +8635,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8649,7 +8653,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>326</v>
@@ -8666,10 +8670,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8695,13 +8699,13 @@
         <v>241</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>333</v>
@@ -8753,7 +8757,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8788,10 +8792,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8875,7 +8879,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8910,10 +8914,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8939,10 +8943,10 @@
         <v>83</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>399</v>
@@ -8997,7 +9001,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
